--- a/Class Work/BO/func_1.xlsx
+++ b/Class Work/BO/func_1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MSE\5820x\Class Work\BO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B4EEB00-647B-48A7-B393-DCB86B27176D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F030EFB-76B6-437F-ABE7-14376262D2DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="270" yWindow="975" windowWidth="20220" windowHeight="10545" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="270" yWindow="375" windowWidth="20220" windowHeight="10545" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Minimize" sheetId="1" r:id="rId1"/>
@@ -356,7 +356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="23.5703125" customWidth="1"/>
@@ -377,48 +377,288 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>1.3</v>
-      </c>
-      <c r="B2">
-        <v>0.3</v>
+      <c r="A2" s="1">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1">
+        <v>0</v>
       </c>
       <c r="C2" s="1">
-        <v>4</v>
-      </c>
-      <c r="D2">
-        <f t="shared" ref="D2:D4" si="0">((A2-2)^2) +((B2+1)^2) + ((C2-0.5)^2)</f>
-        <v>14.43</v>
+        <v>0</v>
+      </c>
+      <c r="D2" s="1">
+        <f>((A2-1)^2) +((B2+2)^2) + ((C2-0.5)^2)</f>
+        <v>5.25</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2.1</v>
-      </c>
-      <c r="B3">
-        <v>-0.1</v>
+      <c r="A3" s="1">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1">
+        <v>2</v>
       </c>
       <c r="C3" s="1">
         <v>3</v>
       </c>
-      <c r="D3">
-        <f t="shared" si="0"/>
-        <v>7.07</v>
+      <c r="D3" s="1">
+        <f t="shared" ref="D3:D20" si="0">((A3-1)^2) +((B3+2)^2) + ((C3-0.5)^2)</f>
+        <v>22.25</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>3.2</v>
-      </c>
-      <c r="B4">
-        <v>0.2</v>
+      <c r="A4" s="1">
+        <v>-1</v>
+      </c>
+      <c r="B4" s="1">
+        <v>3</v>
       </c>
       <c r="C4" s="1">
-        <v>2</v>
-      </c>
-      <c r="D4">
-        <f t="shared" si="0"/>
-        <v>5.1300000000000008</v>
+        <v>0</v>
+      </c>
+      <c r="D4" s="1">
+        <f t="shared" si="0"/>
+        <v>29.25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>-2</v>
+      </c>
+      <c r="B5" s="1">
+        <v>0</v>
+      </c>
+      <c r="C5" s="1">
+        <v>4</v>
+      </c>
+      <c r="D5" s="1">
+        <f t="shared" si="0"/>
+        <v>25.25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>1.756</v>
+      </c>
+      <c r="B6">
+        <v>-4.6440000000000001</v>
+      </c>
+      <c r="C6">
+        <v>1.1359999999999999</v>
+      </c>
+      <c r="D6" s="1">
+        <f t="shared" si="0"/>
+        <v>7.966768000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>-2.3E-2</v>
+      </c>
+      <c r="B7">
+        <v>-0.84199999999999997</v>
+      </c>
+      <c r="C7">
+        <v>1.57</v>
+      </c>
+      <c r="D7" s="1">
+        <f t="shared" si="0"/>
+        <v>3.5323929999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>-3.36</v>
+      </c>
+      <c r="B8">
+        <v>-1.1000000000000001</v>
+      </c>
+      <c r="C8">
+        <v>-2.774</v>
+      </c>
+      <c r="D8" s="1">
+        <f t="shared" si="0"/>
+        <v>30.538675999999995</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>0.35299999999999998</v>
+      </c>
+      <c r="B9">
+        <v>-2.391</v>
+      </c>
+      <c r="C9">
+        <v>6.2E-2</v>
+      </c>
+      <c r="D9" s="1">
+        <f t="shared" si="0"/>
+        <v>0.76333400000000007</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>0.32100000000000001</v>
+      </c>
+      <c r="B10">
+        <v>-2.82</v>
+      </c>
+      <c r="C10">
+        <v>-2.621</v>
+      </c>
+      <c r="D10" s="1">
+        <f t="shared" si="0"/>
+        <v>10.874082</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="B11">
+        <v>-1.4430000000000001</v>
+      </c>
+      <c r="C11">
+        <v>-2.1539999999999999</v>
+      </c>
+      <c r="D11" s="1">
+        <f t="shared" si="0"/>
+        <v>8.2717290000000006</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>0.81599999999999995</v>
+      </c>
+      <c r="B12">
+        <v>-1.504</v>
+      </c>
+      <c r="C12">
+        <v>0.56899999999999995</v>
+      </c>
+      <c r="D12" s="1">
+        <f t="shared" si="0"/>
+        <v>0.28463300000000002</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>0.78300000000000003</v>
+      </c>
+      <c r="B13">
+        <v>-1.631</v>
+      </c>
+      <c r="C13">
+        <v>-0.04</v>
+      </c>
+      <c r="D13" s="1">
+        <f t="shared" si="0"/>
+        <v>0.47484999999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>4.2640000000000002</v>
+      </c>
+      <c r="B14">
+        <v>-1.502</v>
+      </c>
+      <c r="C14">
+        <v>-0.30099999999999999</v>
+      </c>
+      <c r="D14" s="1">
+        <f t="shared" si="0"/>
+        <v>11.543301000000001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>1.361</v>
+      </c>
+      <c r="B15">
+        <v>-2.218</v>
+      </c>
+      <c r="C15">
+        <v>-0.115</v>
+      </c>
+      <c r="D15" s="1">
+        <f t="shared" si="0"/>
+        <v>0.55606999999999995</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>1.5940000000000001</v>
+      </c>
+      <c r="B16">
+        <v>-2.367</v>
+      </c>
+      <c r="C16">
+        <v>0.63100000000000001</v>
+      </c>
+      <c r="D16" s="1">
+        <f t="shared" si="0"/>
+        <v>0.50468600000000008</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>1.179</v>
+      </c>
+      <c r="B17">
+        <v>-2.6230000000000002</v>
+      </c>
+      <c r="C17">
+        <v>0.158</v>
+      </c>
+      <c r="D17" s="1">
+        <f t="shared" si="0"/>
+        <v>0.53713400000000022</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>0.81200000000000006</v>
+      </c>
+      <c r="B18">
+        <v>-3.0990000000000002</v>
+      </c>
+      <c r="C18">
+        <v>1.706</v>
+      </c>
+      <c r="D18" s="1">
+        <f t="shared" si="0"/>
+        <v>2.6975810000000005</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>1.4019999999999999</v>
+      </c>
+      <c r="B19">
+        <v>-1.994</v>
+      </c>
+      <c r="C19">
+        <v>1.425</v>
+      </c>
+      <c r="D19" s="1">
+        <f t="shared" si="0"/>
+        <v>1.0172650000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>1.093</v>
+      </c>
+      <c r="B20">
+        <v>-2.9729999999999999</v>
+      </c>
+      <c r="C20">
+        <v>1.4670000000000001</v>
+      </c>
+      <c r="D20" s="1">
+        <f t="shared" si="0"/>
+        <v>1.8904669999999999</v>
       </c>
     </row>
   </sheetData>
